--- a/data/trans_dic/VUL_MENTALCOM-Clase-trans_dic.xlsx
+++ b/data/trans_dic/VUL_MENTALCOM-Clase-trans_dic.xlsx
@@ -583,40 +583,40 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>0</v>
+        <v>0.04754706792053832</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>0</v>
+        <v>0.113187432708232</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0</v>
+        <v>0.01916796608702186</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>0</v>
+        <v>0.03179301990783422</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>0</v>
+        <v>0.09064065108464453</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>0</v>
+        <v>0.2335697953079745</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>0</v>
+        <v>0.03686331996574192</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>0</v>
+        <v>0.03652990694705572</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>0</v>
+        <v>0.06707739335722597</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>0</v>
+        <v>0.1740664160851157</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>0</v>
+        <v>0.02773851131460108</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>0</v>
+        <v>0.03422022134286856</v>
       </c>
     </row>
     <row r="5">
@@ -626,18 +626,42 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr"/>
-      <c r="D5" s="4" t="inlineStr"/>
-      <c r="E5" s="4" t="inlineStr"/>
-      <c r="F5" s="4" t="inlineStr"/>
-      <c r="G5" s="4" t="inlineStr"/>
-      <c r="H5" s="4" t="inlineStr"/>
-      <c r="I5" s="4" t="inlineStr"/>
-      <c r="J5" s="4" t="inlineStr"/>
-      <c r="K5" s="4" t="inlineStr"/>
-      <c r="L5" s="4" t="inlineStr"/>
-      <c r="M5" s="4" t="inlineStr"/>
-      <c r="N5" s="4" t="inlineStr"/>
+      <c r="C5" s="4" t="n">
+        <v>0.02979213828393286</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>0.08639374832774392</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>0.008738399840375954</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>0.02014772580606563</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>0.06520033081269362</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>0.1975613770131526</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>0.02246247047300794</v>
+      </c>
+      <c r="J5" s="4" t="n">
+        <v>0.02561018952050704</v>
+      </c>
+      <c r="K5" s="4" t="n">
+        <v>0.0497852314310554</v>
+      </c>
+      <c r="L5" s="4" t="n">
+        <v>0.1509240846793346</v>
+      </c>
+      <c r="M5" s="4" t="n">
+        <v>0.01775321902039766</v>
+      </c>
+      <c r="N5" s="4" t="n">
+        <v>0.02585160143055695</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n"/>
@@ -646,18 +670,42 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr"/>
-      <c r="D6" s="4" t="inlineStr"/>
-      <c r="E6" s="4" t="inlineStr"/>
-      <c r="F6" s="4" t="inlineStr"/>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="4" t="inlineStr"/>
-      <c r="I6" s="4" t="inlineStr"/>
-      <c r="J6" s="4" t="inlineStr"/>
-      <c r="K6" s="4" t="inlineStr"/>
-      <c r="L6" s="4" t="inlineStr"/>
-      <c r="M6" s="4" t="inlineStr"/>
-      <c r="N6" s="4" t="inlineStr"/>
+      <c r="C6" s="4" t="n">
+        <v>0.07719692932439329</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>0.14247260611361</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>0.03785421224780781</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>0.04671318854341554</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>0.1229987509425356</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>0.2746526676203937</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>0.06167208916952789</v>
+      </c>
+      <c r="J6" s="4" t="n">
+        <v>0.05113943735223514</v>
+      </c>
+      <c r="K6" s="4" t="n">
+        <v>0.08606261670376995</v>
+      </c>
+      <c r="L6" s="4" t="n">
+        <v>0.1972764747754089</v>
+      </c>
+      <c r="M6" s="4" t="n">
+        <v>0.04032811446280587</v>
+      </c>
+      <c r="N6" s="4" t="n">
+        <v>0.04454533711180286</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -671,40 +719,40 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0</v>
+        <v>0.05712530326444684</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0</v>
+        <v>0.156500173259329</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0</v>
+        <v>0.0415822047894233</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0</v>
+        <v>0.03909450409656665</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0</v>
+        <v>0.09267652388060027</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0</v>
+        <v>0.2504616026945505</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0</v>
+        <v>0.0405574238461127</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0</v>
+        <v>0.05575124060447287</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0</v>
+        <v>0.07357567138236809</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0</v>
+        <v>0.2105274594170272</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0</v>
+        <v>0.04102604819191068</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0</v>
+        <v>0.04872878035665485</v>
       </c>
     </row>
     <row r="8">
@@ -714,18 +762,42 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr"/>
-      <c r="D8" s="4" t="inlineStr"/>
-      <c r="E8" s="4" t="inlineStr"/>
-      <c r="F8" s="4" t="inlineStr"/>
-      <c r="G8" s="4" t="inlineStr"/>
-      <c r="H8" s="4" t="inlineStr"/>
-      <c r="I8" s="4" t="inlineStr"/>
-      <c r="J8" s="4" t="inlineStr"/>
-      <c r="K8" s="4" t="inlineStr"/>
-      <c r="L8" s="4" t="inlineStr"/>
-      <c r="M8" s="4" t="inlineStr"/>
-      <c r="N8" s="4" t="inlineStr"/>
+      <c r="C8" s="4" t="n">
+        <v>0.03462102662422556</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>0.117370631750868</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>0.02207971343466302</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>0.0228049803704516</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>0.06109527814488275</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>0.2092125634817564</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>0.02468115226884625</v>
+      </c>
+      <c r="J8" s="4" t="n">
+        <v>0.03897425135618396</v>
+      </c>
+      <c r="K8" s="4" t="n">
+        <v>0.05508862874688437</v>
+      </c>
+      <c r="L8" s="4" t="n">
+        <v>0.1807828703820078</v>
+      </c>
+      <c r="M8" s="4" t="n">
+        <v>0.02730646518591327</v>
+      </c>
+      <c r="N8" s="4" t="n">
+        <v>0.03431477851790009</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n"/>
@@ -734,18 +806,42 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr"/>
-      <c r="D9" s="4" t="inlineStr"/>
-      <c r="E9" s="4" t="inlineStr"/>
-      <c r="F9" s="4" t="inlineStr"/>
-      <c r="G9" s="4" t="inlineStr"/>
-      <c r="H9" s="4" t="inlineStr"/>
-      <c r="I9" s="4" t="inlineStr"/>
-      <c r="J9" s="4" t="inlineStr"/>
-      <c r="K9" s="4" t="inlineStr"/>
-      <c r="L9" s="4" t="inlineStr"/>
-      <c r="M9" s="4" t="inlineStr"/>
-      <c r="N9" s="4" t="inlineStr"/>
+      <c r="C9" s="4" t="n">
+        <v>0.08943814125282434</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>0.2058440489647264</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>0.07342239304418754</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>0.06073525901026974</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>0.1315449918592261</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>0.3061996094252219</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>0.06790157892300831</v>
+      </c>
+      <c r="J9" s="4" t="n">
+        <v>0.07827365828496581</v>
+      </c>
+      <c r="K9" s="4" t="n">
+        <v>0.0962306785496443</v>
+      </c>
+      <c r="L9" s="4" t="n">
+        <v>0.2447542743524614</v>
+      </c>
+      <c r="M9" s="4" t="n">
+        <v>0.05789700545788686</v>
+      </c>
+      <c r="N9" s="4" t="n">
+        <v>0.06445349429568871</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -759,40 +855,40 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0</v>
+        <v>0.0750610623112416</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0</v>
+        <v>0.2306512379042149</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0</v>
+        <v>0.03926097974673363</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0</v>
+        <v>0.0426137011281105</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0</v>
+        <v>0.1449697989369501</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0</v>
+        <v>0.3400870881032319</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0</v>
+        <v>0.1260293521734491</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0</v>
+        <v>0.1169592089855648</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0</v>
+        <v>0.09638140706915879</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0</v>
+        <v>0.2716693253609195</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0</v>
+        <v>0.06553178433301014</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0</v>
+        <v>0.06433208602239811</v>
       </c>
     </row>
     <row r="11">
@@ -802,18 +898,42 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr"/>
-      <c r="D11" s="4" t="inlineStr"/>
-      <c r="E11" s="4" t="inlineStr"/>
-      <c r="F11" s="4" t="inlineStr"/>
-      <c r="G11" s="4" t="inlineStr"/>
-      <c r="H11" s="4" t="inlineStr"/>
-      <c r="I11" s="4" t="inlineStr"/>
-      <c r="J11" s="4" t="inlineStr"/>
-      <c r="K11" s="4" t="inlineStr"/>
-      <c r="L11" s="4" t="inlineStr"/>
-      <c r="M11" s="4" t="inlineStr"/>
-      <c r="N11" s="4" t="inlineStr"/>
+      <c r="C11" s="4" t="n">
+        <v>0.04667653942110242</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>0.1605842254547248</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>0.02039215904746621</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>0.029664272507463</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>0.09639372653069445</v>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>0.2533991689341181</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>0.06897747112523225</v>
+      </c>
+      <c r="J11" s="4" t="n">
+        <v>0.08578160578790073</v>
+      </c>
+      <c r="K11" s="4" t="n">
+        <v>0.07079176322480012</v>
+      </c>
+      <c r="L11" s="4" t="n">
+        <v>0.2180622838193109</v>
+      </c>
+      <c r="M11" s="4" t="n">
+        <v>0.04282484514301585</v>
+      </c>
+      <c r="N11" s="4" t="n">
+        <v>0.05082507974663295</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n"/>
@@ -822,18 +942,42 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr"/>
-      <c r="D12" s="4" t="inlineStr"/>
-      <c r="E12" s="4" t="inlineStr"/>
-      <c r="F12" s="4" t="inlineStr"/>
-      <c r="G12" s="4" t="inlineStr"/>
-      <c r="H12" s="4" t="inlineStr"/>
-      <c r="I12" s="4" t="inlineStr"/>
-      <c r="J12" s="4" t="inlineStr"/>
-      <c r="K12" s="4" t="inlineStr"/>
-      <c r="L12" s="4" t="inlineStr"/>
-      <c r="M12" s="4" t="inlineStr"/>
-      <c r="N12" s="4" t="inlineStr"/>
+      <c r="C12" s="4" t="n">
+        <v>0.1201086697174404</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>0.3037107127632862</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>0.0746297903052397</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>0.0590567354131041</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>0.2057730681146592</v>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>0.4444270058184346</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>0.2070086625495988</v>
+      </c>
+      <c r="J12" s="4" t="n">
+        <v>0.1602427898355241</v>
+      </c>
+      <c r="K12" s="4" t="n">
+        <v>0.1306444412588375</v>
+      </c>
+      <c r="L12" s="4" t="n">
+        <v>0.3393035927209419</v>
+      </c>
+      <c r="M12" s="4" t="n">
+        <v>0.09395767824124884</v>
+      </c>
+      <c r="N12" s="4" t="n">
+        <v>0.08134784047422773</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -847,40 +991,40 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0</v>
+        <v>0.06763132272575696</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0</v>
+        <v>0.1840213034950926</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0</v>
+        <v>0.02658349405780979</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0</v>
+        <v>0.05662177154053679</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0</v>
+        <v>0.1337278892438776</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0</v>
+        <v>0.3461334824355546</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0</v>
+        <v>0.08258005628281576</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0</v>
+        <v>0.07536838151297087</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0</v>
+        <v>0.09696887614394649</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0</v>
+        <v>0.2640118301515152</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0</v>
+        <v>0.0550725346966894</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0</v>
+        <v>0.06632021048230378</v>
       </c>
     </row>
     <row r="14">
@@ -890,18 +1034,42 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr"/>
-      <c r="D14" s="4" t="inlineStr"/>
-      <c r="E14" s="4" t="inlineStr"/>
-      <c r="F14" s="4" t="inlineStr"/>
-      <c r="G14" s="4" t="inlineStr"/>
-      <c r="H14" s="4" t="inlineStr"/>
-      <c r="I14" s="4" t="inlineStr"/>
-      <c r="J14" s="4" t="inlineStr"/>
-      <c r="K14" s="4" t="inlineStr"/>
-      <c r="L14" s="4" t="inlineStr"/>
-      <c r="M14" s="4" t="inlineStr"/>
-      <c r="N14" s="4" t="inlineStr"/>
+      <c r="C14" s="4" t="n">
+        <v>0.04703337102033517</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>0.1440980559966257</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>0.01340693969825371</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>0.04184138290310877</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>0.1076350908227208</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>0.2880346076140801</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>0.0577826623541316</v>
+      </c>
+      <c r="J14" s="4" t="n">
+        <v>0.05967311668486931</v>
+      </c>
+      <c r="K14" s="4" t="n">
+        <v>0.07988837981070888</v>
+      </c>
+      <c r="L14" s="4" t="n">
+        <v>0.2225519313684555</v>
+      </c>
+      <c r="M14" s="4" t="n">
+        <v>0.03973627128429792</v>
+      </c>
+      <c r="N14" s="4" t="n">
+        <v>0.0548598054084662</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n"/>
@@ -910,18 +1078,42 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr"/>
-      <c r="D15" s="4" t="inlineStr"/>
-      <c r="E15" s="4" t="inlineStr"/>
-      <c r="F15" s="4" t="inlineStr"/>
-      <c r="G15" s="4" t="inlineStr"/>
-      <c r="H15" s="4" t="inlineStr"/>
-      <c r="I15" s="4" t="inlineStr"/>
-      <c r="J15" s="4" t="inlineStr"/>
-      <c r="K15" s="4" t="inlineStr"/>
-      <c r="L15" s="4" t="inlineStr"/>
-      <c r="M15" s="4" t="inlineStr"/>
-      <c r="N15" s="4" t="inlineStr"/>
+      <c r="C15" s="4" t="n">
+        <v>0.09917932373759421</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>0.2327667387595759</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>0.04892336471330441</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>0.07473202511780856</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>0.1672789684167655</v>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>0.4143915714516504</v>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>0.1114374360775296</v>
+      </c>
+      <c r="J15" s="4" t="n">
+        <v>0.09504843836757269</v>
+      </c>
+      <c r="K15" s="4" t="n">
+        <v>0.1149130342838407</v>
+      </c>
+      <c r="L15" s="4" t="n">
+        <v>0.3030648860160522</v>
+      </c>
+      <c r="M15" s="4" t="n">
+        <v>0.0735184653485076</v>
+      </c>
+      <c r="N15" s="4" t="n">
+        <v>0.08098858373993603</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -935,40 +1127,40 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0</v>
+        <v>0.07227716278719204</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0</v>
+        <v>0.0988658350483881</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0</v>
+        <v>0.04757346102228473</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0</v>
+        <v>0.01902451446702437</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0</v>
+        <v>0.1926943275686335</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0</v>
+        <v>0.3224885671445833</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0</v>
+        <v>0.06555360773085121</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0</v>
+        <v>0.09308723469937014</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0</v>
+        <v>0.1483867574416027</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0</v>
+        <v>0.2414181239521144</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0</v>
+        <v>0.05660767062235002</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0</v>
+        <v>0.0661986232286511</v>
       </c>
     </row>
     <row r="17">
@@ -978,18 +1170,42 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr"/>
-      <c r="D17" s="4" t="inlineStr"/>
-      <c r="E17" s="4" t="inlineStr"/>
-      <c r="F17" s="4" t="inlineStr"/>
-      <c r="G17" s="4" t="inlineStr"/>
-      <c r="H17" s="4" t="inlineStr"/>
-      <c r="I17" s="4" t="inlineStr"/>
-      <c r="J17" s="4" t="inlineStr"/>
-      <c r="K17" s="4" t="inlineStr"/>
-      <c r="L17" s="4" t="inlineStr"/>
-      <c r="M17" s="4" t="inlineStr"/>
-      <c r="N17" s="4" t="inlineStr"/>
+      <c r="C17" s="4" t="n">
+        <v>0.03832671230870233</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>0.04896358566313333</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>0.02504022126785758</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>0.008680124061845686</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>0.1597756046038662</v>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>0.2479758123170872</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>0.03621076909000417</v>
+      </c>
+      <c r="J17" s="4" t="n">
+        <v>0.07169611357317097</v>
+      </c>
+      <c r="K17" s="4" t="n">
+        <v>0.1227385493851166</v>
+      </c>
+      <c r="L17" s="4" t="n">
+        <v>0.1900589574295446</v>
+      </c>
+      <c r="M17" s="4" t="n">
+        <v>0.03697615489142295</v>
+      </c>
+      <c r="N17" s="4" t="n">
+        <v>0.05100035410841716</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n"/>
@@ -998,18 +1214,42 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr"/>
-      <c r="D18" s="4" t="inlineStr"/>
-      <c r="E18" s="4" t="inlineStr"/>
-      <c r="F18" s="4" t="inlineStr"/>
-      <c r="G18" s="4" t="inlineStr"/>
-      <c r="H18" s="4" t="inlineStr"/>
-      <c r="I18" s="4" t="inlineStr"/>
-      <c r="J18" s="4" t="inlineStr"/>
-      <c r="K18" s="4" t="inlineStr"/>
-      <c r="L18" s="4" t="inlineStr"/>
-      <c r="M18" s="4" t="inlineStr"/>
-      <c r="N18" s="4" t="inlineStr"/>
+      <c r="C18" s="4" t="n">
+        <v>0.1190231249362927</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>0.16428033362988</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>0.08785078925486689</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>0.03914587699624995</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>0.229328976410983</v>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>0.4173061968196176</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>0.1110299421016453</v>
+      </c>
+      <c r="J18" s="4" t="n">
+        <v>0.1183733896317284</v>
+      </c>
+      <c r="K18" s="4" t="n">
+        <v>0.1767582564556725</v>
+      </c>
+      <c r="L18" s="4" t="n">
+        <v>0.310444494327109</v>
+      </c>
+      <c r="M18" s="4" t="n">
+        <v>0.08249477385061087</v>
+      </c>
+      <c r="N18" s="4" t="n">
+        <v>0.08395950877309263</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -1023,40 +1263,40 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0</v>
+        <v>0.07495135930507799</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0</v>
+        <v>0.1454303788523834</v>
       </c>
       <c r="E19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0</v>
+        <v>0.02032219480471135</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0</v>
+        <v>0.1285980479774671</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0</v>
+        <v>0.2433751321372259</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0</v>
+        <v>0.1148417037376205</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0</v>
+        <v>0.08566398392072909</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0</v>
+        <v>0.1156762598387376</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0</v>
+        <v>0.2072128908708177</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0</v>
+        <v>0.06154499532336427</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0</v>
+        <v>0.06559049704693948</v>
       </c>
     </row>
     <row r="20">
@@ -1066,18 +1306,40 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr"/>
-      <c r="D20" s="4" t="inlineStr"/>
+      <c r="C20" s="4" t="n">
+        <v>0.02987890312757071</v>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>0.06342638003480262</v>
+      </c>
       <c r="E20" s="4" t="inlineStr"/>
-      <c r="F20" s="4" t="inlineStr"/>
-      <c r="G20" s="4" t="inlineStr"/>
-      <c r="H20" s="4" t="inlineStr"/>
-      <c r="I20" s="4" t="inlineStr"/>
-      <c r="J20" s="4" t="inlineStr"/>
-      <c r="K20" s="4" t="inlineStr"/>
-      <c r="L20" s="4" t="inlineStr"/>
-      <c r="M20" s="4" t="inlineStr"/>
-      <c r="N20" s="4" t="inlineStr"/>
+      <c r="F20" s="4" t="n">
+        <v>0.005825321370696296</v>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>0.09895900567270643</v>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>0.1751993913071447</v>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="4" t="n">
+        <v>0.06466281597590744</v>
+      </c>
+      <c r="K20" s="4" t="n">
+        <v>0.09241394957666722</v>
+      </c>
+      <c r="L20" s="4" t="n">
+        <v>0.1529643985051731</v>
+      </c>
+      <c r="M20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="4" t="n">
+        <v>0.04988532166994088</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n"/>
@@ -1086,18 +1348,40 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr"/>
-      <c r="D21" s="4" t="inlineStr"/>
+      <c r="C21" s="4" t="n">
+        <v>0.1567910124800309</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>0.2983948158145771</v>
+      </c>
       <c r="E21" s="4" t="inlineStr"/>
-      <c r="F21" s="4" t="inlineStr"/>
-      <c r="G21" s="4" t="inlineStr"/>
-      <c r="H21" s="4" t="inlineStr"/>
-      <c r="I21" s="4" t="inlineStr"/>
-      <c r="J21" s="4" t="inlineStr"/>
-      <c r="K21" s="4" t="inlineStr"/>
-      <c r="L21" s="4" t="inlineStr"/>
-      <c r="M21" s="4" t="inlineStr"/>
-      <c r="N21" s="4" t="inlineStr"/>
+      <c r="F21" s="4" t="n">
+        <v>0.05484705949843285</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>0.1628127023081129</v>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>0.3289058937241521</v>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>0.4518458987086745</v>
+      </c>
+      <c r="J21" s="4" t="n">
+        <v>0.1101305230556734</v>
+      </c>
+      <c r="K21" s="4" t="n">
+        <v>0.1496703716121248</v>
+      </c>
+      <c r="L21" s="4" t="n">
+        <v>0.2827539445386937</v>
+      </c>
+      <c r="M21" s="4" t="n">
+        <v>0.3461111566036721</v>
+      </c>
+      <c r="N21" s="4" t="n">
+        <v>0.08310252140536588</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
@@ -1111,40 +1395,40 @@
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0</v>
+        <v>0.06364544613779359</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0</v>
+        <v>0.1552979242367809</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0</v>
+        <v>0.03159097243881275</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0</v>
+        <v>0.03890968563636312</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0</v>
+        <v>0.1306516400353701</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0</v>
+        <v>0.2812252769524416</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0</v>
+        <v>0.06193103077173319</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0</v>
+        <v>0.07154996264186</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0</v>
+        <v>0.09822672999286539</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0</v>
+        <v>0.221465897730391</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0</v>
+        <v>0.04628828557998438</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0</v>
+        <v>0.05619870012728082</v>
       </c>
     </row>
     <row r="23">
@@ -1154,18 +1438,42 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr"/>
-      <c r="D23" s="4" t="inlineStr"/>
-      <c r="E23" s="4" t="inlineStr"/>
-      <c r="F23" s="4" t="inlineStr"/>
-      <c r="G23" s="4" t="inlineStr"/>
-      <c r="H23" s="4" t="inlineStr"/>
-      <c r="I23" s="4" t="inlineStr"/>
-      <c r="J23" s="4" t="inlineStr"/>
-      <c r="K23" s="4" t="inlineStr"/>
-      <c r="L23" s="4" t="inlineStr"/>
-      <c r="M23" s="4" t="inlineStr"/>
-      <c r="N23" s="4" t="inlineStr"/>
+      <c r="C23" s="4" t="n">
+        <v>0.05147087709373428</v>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>0.1350827802277075</v>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>0.02433864033005191</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>0.03264322252745321</v>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>0.1188239191339142</v>
+      </c>
+      <c r="H23" s="4" t="n">
+        <v>0.2581750815977503</v>
+      </c>
+      <c r="I23" s="4" t="n">
+        <v>0.05004900776123812</v>
+      </c>
+      <c r="J23" s="4" t="n">
+        <v>0.06367189249089765</v>
+      </c>
+      <c r="K23" s="4" t="n">
+        <v>0.08872202811667151</v>
+      </c>
+      <c r="L23" s="4" t="n">
+        <v>0.2040279581956867</v>
+      </c>
+      <c r="M23" s="4" t="n">
+        <v>0.03907902602743623</v>
+      </c>
+      <c r="N23" s="4" t="n">
+        <v>0.05092214985975309</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n"/>
@@ -1174,18 +1482,42 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr"/>
-      <c r="D24" s="4" t="inlineStr"/>
-      <c r="E24" s="4" t="inlineStr"/>
-      <c r="F24" s="4" t="inlineStr"/>
-      <c r="G24" s="4" t="inlineStr"/>
-      <c r="H24" s="4" t="inlineStr"/>
-      <c r="I24" s="4" t="inlineStr"/>
-      <c r="J24" s="4" t="inlineStr"/>
-      <c r="K24" s="4" t="inlineStr"/>
-      <c r="L24" s="4" t="inlineStr"/>
-      <c r="M24" s="4" t="inlineStr"/>
-      <c r="N24" s="4" t="inlineStr"/>
+      <c r="C24" s="4" t="n">
+        <v>0.07570815393954997</v>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>0.1768537034480434</v>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>0.04210794934509481</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>0.04587724330122223</v>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>0.1452987901765066</v>
+      </c>
+      <c r="H24" s="4" t="n">
+        <v>0.3052964302892714</v>
+      </c>
+      <c r="I24" s="4" t="n">
+        <v>0.07583043786646537</v>
+      </c>
+      <c r="J24" s="4" t="n">
+        <v>0.07992082427652178</v>
+      </c>
+      <c r="K24" s="4" t="n">
+        <v>0.1081538543160996</v>
+      </c>
+      <c r="L24" s="4" t="n">
+        <v>0.2379781162413396</v>
+      </c>
+      <c r="M24" s="4" t="n">
+        <v>0.0543382342474485</v>
+      </c>
+      <c r="N24" s="4" t="n">
+        <v>0.06149712075070862</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1361,40 +1693,40 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>0</v>
+        <v>148</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5">
@@ -1405,40 +1737,40 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>0</v>
+        <v>17806</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>0</v>
+        <v>23276</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0</v>
+        <v>5134</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0</v>
+        <v>4656</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0</v>
+        <v>28135</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>0</v>
+        <v>49142</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>0</v>
+        <v>9275</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>0</v>
+        <v>5622</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>0</v>
+        <v>45941</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>0</v>
+        <v>72418</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>0</v>
+        <v>14409</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>0</v>
+        <v>10279</v>
       </c>
     </row>
     <row r="6">
@@ -1448,18 +1780,42 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr"/>
-      <c r="K6" s="5" t="inlineStr"/>
-      <c r="L6" s="5" t="inlineStr"/>
-      <c r="M6" s="5" t="inlineStr"/>
-      <c r="N6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="n">
+        <v>11157</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>17766</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>2341</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>2951</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>20238</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>41566</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>5651</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>3942</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>34098</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>62790</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>9222</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>7765</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n"/>
@@ -1468,18 +1824,42 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr"/>
-      <c r="D7" s="5" t="inlineStr"/>
-      <c r="E7" s="5" t="inlineStr"/>
-      <c r="F7" s="5" t="inlineStr"/>
-      <c r="G7" s="5" t="inlineStr"/>
-      <c r="H7" s="5" t="inlineStr"/>
-      <c r="I7" s="5" t="inlineStr"/>
-      <c r="J7" s="5" t="inlineStr"/>
-      <c r="K7" s="5" t="inlineStr"/>
-      <c r="L7" s="5" t="inlineStr"/>
-      <c r="M7" s="5" t="inlineStr"/>
-      <c r="N7" s="5" t="inlineStr"/>
+      <c r="C7" s="5" t="n">
+        <v>28910</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>29298</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>10140</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>6842</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>38179</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>57786</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>15516</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>7871</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>58944</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>82075</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>20949</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>13380</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -1493,40 +1873,40 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>0</v>
+        <v>161</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="N8" s="5" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9">
@@ -1537,40 +1917,40 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>0</v>
+        <v>17638</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>0</v>
+        <v>19554</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0</v>
+        <v>7149</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0</v>
+        <v>3229</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0</v>
+        <v>24644</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>0</v>
+        <v>42339</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>0</v>
+        <v>8275</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>0</v>
+        <v>6318</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>0</v>
+        <v>42282</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>0</v>
+        <v>61893</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>0</v>
+        <v>15424</v>
       </c>
       <c r="N9" s="5" t="n">
-        <v>0</v>
+        <v>9547</v>
       </c>
     </row>
     <row r="10">
@@ -1580,18 +1960,42 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="inlineStr"/>
-      <c r="F10" s="5" t="inlineStr"/>
-      <c r="G10" s="5" t="inlineStr"/>
-      <c r="H10" s="5" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr"/>
-      <c r="J10" s="5" t="inlineStr"/>
-      <c r="K10" s="5" t="inlineStr"/>
-      <c r="L10" s="5" t="inlineStr"/>
-      <c r="M10" s="5" t="inlineStr"/>
-      <c r="N10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="n">
+        <v>10690</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>14665</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>3796</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>1884</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>16246</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>35366</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>5036</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>4417</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>31658</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>53148</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>10266</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>6723</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n"/>
@@ -1600,18 +2004,42 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="5" t="inlineStr"/>
-      <c r="G11" s="5" t="inlineStr"/>
-      <c r="H11" s="5" t="inlineStr"/>
-      <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="5" t="inlineStr"/>
-      <c r="K11" s="5" t="inlineStr"/>
-      <c r="L11" s="5" t="inlineStr"/>
-      <c r="M11" s="5" t="inlineStr"/>
-      <c r="N11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="n">
+        <v>27615</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>25720</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>12623</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>5017</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>34980</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>51761</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>13854</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>8870</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>55301</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>71955</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>21766</v>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>12628</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1625,40 +2053,40 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N12" s="5" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13">
@@ -1669,40 +2097,40 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>0</v>
+        <v>17066</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>0</v>
+        <v>22085</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>0</v>
+        <v>6012</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0</v>
+        <v>5804</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0</v>
+        <v>14463</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>0</v>
+        <v>19522</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>0</v>
+        <v>8380</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>0</v>
+        <v>6575</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>0</v>
+        <v>31529</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>0</v>
+        <v>41607</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>0</v>
+        <v>14392</v>
       </c>
       <c r="N13" s="5" t="n">
-        <v>0</v>
+        <v>12379</v>
       </c>
     </row>
     <row r="14">
@@ -1712,18 +2140,42 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr"/>
-      <c r="D14" s="5" t="inlineStr"/>
-      <c r="E14" s="5" t="inlineStr"/>
-      <c r="F14" s="5" t="inlineStr"/>
-      <c r="G14" s="5" t="inlineStr"/>
-      <c r="H14" s="5" t="inlineStr"/>
-      <c r="I14" s="5" t="inlineStr"/>
-      <c r="J14" s="5" t="inlineStr"/>
-      <c r="K14" s="5" t="inlineStr"/>
-      <c r="L14" s="5" t="inlineStr"/>
-      <c r="M14" s="5" t="inlineStr"/>
-      <c r="N14" s="5" t="inlineStr"/>
+      <c r="C14" s="5" t="n">
+        <v>10612</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>15376</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>3122</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>4041</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>9617</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>14546</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>4586</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>4822</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>23158</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>33397</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>9405</v>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>9780</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n"/>
@@ -1732,18 +2184,42 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr"/>
-      <c r="D15" s="5" t="inlineStr"/>
-      <c r="E15" s="5" t="inlineStr"/>
-      <c r="F15" s="5" t="inlineStr"/>
-      <c r="G15" s="5" t="inlineStr"/>
-      <c r="H15" s="5" t="inlineStr"/>
-      <c r="I15" s="5" t="inlineStr"/>
-      <c r="J15" s="5" t="inlineStr"/>
-      <c r="K15" s="5" t="inlineStr"/>
-      <c r="L15" s="5" t="inlineStr"/>
-      <c r="M15" s="5" t="inlineStr"/>
-      <c r="N15" s="5" t="inlineStr"/>
+      <c r="C15" s="5" t="n">
+        <v>27308</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>29080</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>11427</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>8044</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>20529</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>25512</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>13764</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>9008</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>42737</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>51966</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>20634</v>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>15653</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -1757,40 +2233,40 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>0</v>
+        <v>179</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="N16" s="5" t="n">
-        <v>0</v>
+        <v>121</v>
       </c>
     </row>
     <row r="17">
@@ -1801,40 +2277,40 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>0</v>
+        <v>35459</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>0</v>
+        <v>30022</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>0</v>
+        <v>6875</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>0</v>
+        <v>8691</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0</v>
+        <v>55958</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>0</v>
+        <v>55003</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>0</v>
+        <v>22118</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>0</v>
+        <v>12399</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>0</v>
+        <v>91418</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>0</v>
+        <v>85025</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>0</v>
+        <v>28993</v>
       </c>
       <c r="N17" s="5" t="n">
-        <v>0</v>
+        <v>21090</v>
       </c>
     </row>
     <row r="18">
@@ -1844,18 +2320,42 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr"/>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="inlineStr"/>
-      <c r="F18" s="5" t="inlineStr"/>
-      <c r="G18" s="5" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr"/>
-      <c r="J18" s="5" t="inlineStr"/>
-      <c r="K18" s="5" t="inlineStr"/>
-      <c r="L18" s="5" t="inlineStr"/>
-      <c r="M18" s="5" t="inlineStr"/>
-      <c r="N18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="n">
+        <v>24660</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>23508</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>3467</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>6422</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>45040</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>45771</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>15477</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>9817</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>75315</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>71673</v>
+      </c>
+      <c r="M18" s="5" t="n">
+        <v>20920</v>
+      </c>
+      <c r="N18" s="5" t="n">
+        <v>17446</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n"/>
@@ -1864,18 +2364,42 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr"/>
-      <c r="D19" s="5" t="inlineStr"/>
-      <c r="E19" s="5" t="inlineStr"/>
-      <c r="F19" s="5" t="inlineStr"/>
-      <c r="G19" s="5" t="inlineStr"/>
-      <c r="H19" s="5" t="inlineStr"/>
-      <c r="I19" s="5" t="inlineStr"/>
-      <c r="J19" s="5" t="inlineStr"/>
-      <c r="K19" s="5" t="inlineStr"/>
-      <c r="L19" s="5" t="inlineStr"/>
-      <c r="M19" s="5" t="inlineStr"/>
-      <c r="N19" s="5" t="inlineStr"/>
+      <c r="C19" s="5" t="n">
+        <v>52000</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>37974</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>12652</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>11470</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>69998</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>65850</v>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>29848</v>
+      </c>
+      <c r="J19" s="5" t="n">
+        <v>15637</v>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>108335</v>
+      </c>
+      <c r="L19" s="5" t="n">
+        <v>97602</v>
+      </c>
+      <c r="M19" s="5" t="n">
+        <v>38704</v>
+      </c>
+      <c r="N19" s="5" t="n">
+        <v>25755</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -1889,40 +2413,40 @@
         </is>
       </c>
       <c r="C20" s="5" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N20" s="5" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
     </row>
     <row r="21">
@@ -1933,40 +2457,40 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>0</v>
+        <v>14080</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>0</v>
+        <v>5310</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>0</v>
+        <v>5810</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>0</v>
+        <v>1218</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0</v>
+        <v>64480</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>0</v>
+        <v>30456</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>0</v>
+        <v>8085</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>0</v>
+        <v>10455</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>0</v>
+        <v>78559</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>0</v>
+        <v>35766</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>0</v>
+        <v>13896</v>
       </c>
       <c r="N21" s="5" t="n">
-        <v>0</v>
+        <v>11673</v>
       </c>
     </row>
     <row r="22">
@@ -1976,18 +2500,42 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr"/>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="5" t="inlineStr"/>
-      <c r="G22" s="5" t="inlineStr"/>
-      <c r="H22" s="5" t="inlineStr"/>
-      <c r="I22" s="5" t="inlineStr"/>
-      <c r="J22" s="5" t="inlineStr"/>
-      <c r="K22" s="5" t="inlineStr"/>
-      <c r="L22" s="5" t="inlineStr"/>
-      <c r="M22" s="5" t="inlineStr"/>
-      <c r="N22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="n">
+        <v>7466</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>2630</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>3058</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>556</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>53464</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>23419</v>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>4466</v>
+      </c>
+      <c r="J22" s="5" t="n">
+        <v>8052</v>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>64981</v>
+      </c>
+      <c r="L22" s="5" t="n">
+        <v>28157</v>
+      </c>
+      <c r="M22" s="5" t="n">
+        <v>9077</v>
+      </c>
+      <c r="N22" s="5" t="n">
+        <v>8993</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n"/>
@@ -1996,18 +2544,42 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr"/>
-      <c r="D23" s="5" t="inlineStr"/>
-      <c r="E23" s="5" t="inlineStr"/>
-      <c r="F23" s="5" t="inlineStr"/>
-      <c r="G23" s="5" t="inlineStr"/>
-      <c r="H23" s="5" t="inlineStr"/>
-      <c r="I23" s="5" t="inlineStr"/>
-      <c r="J23" s="5" t="inlineStr"/>
-      <c r="K23" s="5" t="inlineStr"/>
-      <c r="L23" s="5" t="inlineStr"/>
-      <c r="M23" s="5" t="inlineStr"/>
-      <c r="N23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="n">
+        <v>23186</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>8823</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>10729</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>2506</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>76738</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>39411</v>
+      </c>
+      <c r="I23" s="5" t="n">
+        <v>13694</v>
+      </c>
+      <c r="J23" s="5" t="n">
+        <v>13295</v>
+      </c>
+      <c r="K23" s="5" t="n">
+        <v>93580</v>
+      </c>
+      <c r="L23" s="5" t="n">
+        <v>45992</v>
+      </c>
+      <c r="M23" s="5" t="n">
+        <v>20250</v>
+      </c>
+      <c r="N23" s="5" t="n">
+        <v>14804</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
@@ -2021,40 +2593,40 @@
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E24" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="H24" s="5" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N24" s="5" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
     </row>
     <row r="25">
@@ -2065,40 +2637,40 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>0</v>
+        <v>11105</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>0</v>
+        <v>5315</v>
       </c>
       <c r="E25" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>0</v>
+        <v>1009</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0</v>
+        <v>60052</v>
       </c>
       <c r="H25" s="5" t="n">
-        <v>0</v>
+        <v>15197</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>0</v>
+        <v>929</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>0</v>
+        <v>9594</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>0</v>
+        <v>71158</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>0</v>
+        <v>20512</v>
       </c>
       <c r="M25" s="5" t="n">
-        <v>0</v>
+        <v>929</v>
       </c>
       <c r="N25" s="5" t="n">
-        <v>0</v>
+        <v>10603</v>
       </c>
     </row>
     <row r="26">
@@ -2108,18 +2680,40 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr"/>
-      <c r="D26" s="5" t="inlineStr"/>
+      <c r="C26" s="5" t="n">
+        <v>4427</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>2318</v>
+      </c>
       <c r="E26" s="5" t="inlineStr"/>
-      <c r="F26" s="5" t="inlineStr"/>
-      <c r="G26" s="5" t="inlineStr"/>
-      <c r="H26" s="5" t="inlineStr"/>
-      <c r="I26" s="5" t="inlineStr"/>
-      <c r="J26" s="5" t="inlineStr"/>
-      <c r="K26" s="5" t="inlineStr"/>
-      <c r="L26" s="5" t="inlineStr"/>
-      <c r="M26" s="5" t="inlineStr"/>
-      <c r="N26" s="5" t="inlineStr"/>
+      <c r="F26" s="5" t="n">
+        <v>289</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>46212</v>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>10940</v>
+      </c>
+      <c r="I26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="5" t="n">
+        <v>7242</v>
+      </c>
+      <c r="K26" s="5" t="n">
+        <v>56848</v>
+      </c>
+      <c r="L26" s="5" t="n">
+        <v>15142</v>
+      </c>
+      <c r="M26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" s="5" t="n">
+        <v>8064</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n"/>
@@ -2128,18 +2722,40 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr"/>
-      <c r="D27" s="5" t="inlineStr"/>
+      <c r="C27" s="5" t="n">
+        <v>23232</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>10905</v>
+      </c>
       <c r="E27" s="5" t="inlineStr"/>
-      <c r="F27" s="5" t="inlineStr"/>
-      <c r="G27" s="5" t="inlineStr"/>
-      <c r="H27" s="5" t="inlineStr"/>
-      <c r="I27" s="5" t="inlineStr"/>
-      <c r="J27" s="5" t="inlineStr"/>
-      <c r="K27" s="5" t="inlineStr"/>
-      <c r="L27" s="5" t="inlineStr"/>
-      <c r="M27" s="5" t="inlineStr"/>
-      <c r="N27" s="5" t="inlineStr"/>
+      <c r="F27" s="5" t="n">
+        <v>2724</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>76030</v>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>20537</v>
+      </c>
+      <c r="I27" s="5" t="n">
+        <v>3657</v>
+      </c>
+      <c r="J27" s="5" t="n">
+        <v>12334</v>
+      </c>
+      <c r="K27" s="5" t="n">
+        <v>92069</v>
+      </c>
+      <c r="L27" s="5" t="n">
+        <v>27989</v>
+      </c>
+      <c r="M27" s="5" t="n">
+        <v>5227</v>
+      </c>
+      <c r="N27" s="5" t="n">
+        <v>13434</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
@@ -2153,40 +2769,40 @@
         </is>
       </c>
       <c r="C28" s="5" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>0</v>
+        <v>260</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0</v>
+        <v>349</v>
       </c>
       <c r="H28" s="5" t="n">
-        <v>0</v>
+        <v>509</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>0</v>
+        <v>298</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>0</v>
+        <v>459</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>0</v>
+        <v>769</v>
       </c>
       <c r="M28" s="5" t="n">
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="N28" s="5" t="n">
-        <v>0</v>
+        <v>434</v>
       </c>
     </row>
     <row r="29">
@@ -2197,40 +2813,40 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>0</v>
+        <v>113155</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>0</v>
+        <v>105562</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>0</v>
+        <v>30980</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>0</v>
+        <v>24608</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0</v>
+        <v>247732</v>
       </c>
       <c r="H29" s="5" t="n">
-        <v>0</v>
+        <v>211659</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>0</v>
+        <v>57063</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>0</v>
+        <v>50963</v>
       </c>
       <c r="K29" s="5" t="n">
-        <v>0</v>
+        <v>360887</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>0</v>
+        <v>317221</v>
       </c>
       <c r="M29" s="5" t="n">
-        <v>0</v>
+        <v>88043</v>
       </c>
       <c r="N29" s="5" t="n">
-        <v>0</v>
+        <v>75570</v>
       </c>
     </row>
     <row r="30">
@@ -2240,18 +2856,42 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr"/>
-      <c r="D30" s="5" t="inlineStr"/>
-      <c r="E30" s="5" t="inlineStr"/>
-      <c r="F30" s="5" t="inlineStr"/>
-      <c r="G30" s="5" t="inlineStr"/>
-      <c r="H30" s="5" t="inlineStr"/>
-      <c r="I30" s="5" t="inlineStr"/>
-      <c r="J30" s="5" t="inlineStr"/>
-      <c r="K30" s="5" t="inlineStr"/>
-      <c r="L30" s="5" t="inlineStr"/>
-      <c r="M30" s="5" t="inlineStr"/>
-      <c r="N30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="n">
+        <v>91510</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>91821</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>23868</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>20645</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>225305</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>194311</v>
+      </c>
+      <c r="I30" s="5" t="n">
+        <v>46115</v>
+      </c>
+      <c r="J30" s="5" t="n">
+        <v>45351</v>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>325967</v>
+      </c>
+      <c r="L30" s="5" t="n">
+        <v>292244</v>
+      </c>
+      <c r="M30" s="5" t="n">
+        <v>74330</v>
+      </c>
+      <c r="N30" s="5" t="n">
+        <v>68475</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n"/>
@@ -2260,18 +2900,42 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr"/>
-      <c r="D31" s="5" t="inlineStr"/>
-      <c r="E31" s="5" t="inlineStr"/>
-      <c r="F31" s="5" t="inlineStr"/>
-      <c r="G31" s="5" t="inlineStr"/>
-      <c r="H31" s="5" t="inlineStr"/>
-      <c r="I31" s="5" t="inlineStr"/>
-      <c r="J31" s="5" t="inlineStr"/>
-      <c r="K31" s="5" t="inlineStr"/>
-      <c r="L31" s="5" t="inlineStr"/>
-      <c r="M31" s="5" t="inlineStr"/>
-      <c r="N31" s="5" t="inlineStr"/>
+      <c r="C31" s="5" t="n">
+        <v>134601</v>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>120214</v>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>41294</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>29014</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>275505</v>
+      </c>
+      <c r="H31" s="5" t="n">
+        <v>229776</v>
+      </c>
+      <c r="I31" s="5" t="n">
+        <v>69869</v>
+      </c>
+      <c r="J31" s="5" t="n">
+        <v>56925</v>
+      </c>
+      <c r="K31" s="5" t="n">
+        <v>397359</v>
+      </c>
+      <c r="L31" s="5" t="n">
+        <v>340873</v>
+      </c>
+      <c r="M31" s="5" t="n">
+        <v>103354</v>
+      </c>
+      <c r="N31" s="5" t="n">
+        <v>82695</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
